--- a/Team-Data/2009-10/4-1-2009-10.xlsx
+++ b/Team-Data/2009-10/4-1-2009-10.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,64 +728,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J2" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L2" t="n">
         <v>6.4</v>
       </c>
       <c r="M2" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O2" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>23.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R2" t="n">
         <v>11.8</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T2" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U2" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
         <v>11.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="X2" t="n">
         <v>4.9</v>
@@ -727,25 +794,25 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.9</v>
+        <v>102.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
         <v>7</v>
@@ -757,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>10</v>
@@ -769,25 +836,25 @@
         <v>14</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -796,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>16</v>
@@ -811,7 +878,7 @@
         <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -843,52 +910,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.625</v>
+        <v>0.635</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.482</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="O3" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P3" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
         <v>38.7</v>
@@ -903,25 +970,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
         <v>21.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>9</v>
@@ -936,7 +1003,7 @@
         <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,13 +1012,13 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
         <v>15</v>
@@ -960,13 +1027,13 @@
         <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -975,13 +1042,13 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
         <v>39</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J4" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
         <v>5.6</v>
@@ -1055,28 +1122,28 @@
         <v>16.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P4" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.743</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
         <v>30.5</v>
       </c>
       <c r="T4" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
         <v>15.8</v>
@@ -1097,19 +1164,19 @@
         <v>22.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.7</v>
+        <v>95.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
@@ -1124,28 +1191,28 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>17</v>
@@ -1163,22 +1230,22 @@
         <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1297,7 +1364,7 @@
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>17</v>
@@ -1318,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>19</v>
@@ -1336,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
         <v>17</v>
@@ -1348,19 +1415,19 @@
         <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
         <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB5" t="n">
         <v>23</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="J6" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.49</v>
+        <v>0.487</v>
       </c>
       <c r="L6" t="n">
         <v>7.4</v>
@@ -1422,10 +1489,10 @@
         <v>0.385</v>
       </c>
       <c r="O6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0.721</v>
@@ -1440,34 +1507,34 @@
         <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V6" t="n">
         <v>14</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X6" t="n">
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.4</v>
+        <v>102.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1479,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
         <v>15</v>
@@ -1500,10 +1567,10 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>30</v>
@@ -1521,13 +1588,13 @@
         <v>5</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>2</v>
@@ -1539,7 +1606,7 @@
         <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1656,7 @@
         <v>38.4</v>
       </c>
       <c r="J7" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K7" t="n">
         <v>0.464</v>
@@ -1598,22 +1665,22 @@
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O7" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P7" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S7" t="n">
         <v>31.6</v>
@@ -1622,16 +1689,16 @@
         <v>41.9</v>
       </c>
       <c r="U7" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V7" t="n">
         <v>12.9</v>
       </c>
       <c r="W7" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.2</v>
@@ -1640,16 +1707,16 @@
         <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
@@ -1664,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
         <v>14</v>
@@ -1676,13 +1743,13 @@
         <v>10</v>
       </c>
       <c r="AM7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN7" t="n">
         <v>4</v>
       </c>
       <c r="AO7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
@@ -1700,7 +1767,7 @@
         <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
         <v>3</v>
@@ -1709,19 +1776,19 @@
         <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1838,7 @@
         <v>38.2</v>
       </c>
       <c r="J8" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
@@ -1780,28 +1847,28 @@
         <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O8" t="n">
         <v>23.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R8" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S8" t="n">
         <v>30.7</v>
       </c>
       <c r="T8" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U8" t="n">
         <v>21.1</v>
@@ -1813,28 +1880,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
         <v>5.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.8</v>
+        <v>106.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
@@ -1843,25 +1910,25 @@
         <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
         <v>12</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>15</v>
@@ -1888,16 +1955,16 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>0.301</v>
+        <v>0.311</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,10 +2020,10 @@
         <v>35.7</v>
       </c>
       <c r="J9" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L9" t="n">
         <v>4.4</v>
@@ -1965,7 +2032,7 @@
         <v>14.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="O9" t="n">
         <v>17.7</v>
@@ -1974,10 +2041,10 @@
         <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.726</v>
+        <v>0.723</v>
       </c>
       <c r="R9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S9" t="n">
         <v>27.7</v>
@@ -1992,28 +2059,28 @@
         <v>13.8</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
         <v>3.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z9" t="n">
         <v>22.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB9" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6</v>
+        <v>-5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>26</v>
@@ -2040,7 +2107,7 @@
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN9" t="n">
         <v>30</v>
@@ -2052,10 +2119,10 @@
         <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2064,7 +2131,7 @@
         <v>23</v>
       </c>
       <c r="AU9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -2117,49 +2184,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
         <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>0.288</v>
+        <v>0.284</v>
       </c>
       <c r="H10" t="n">
         <v>48.1</v>
       </c>
       <c r="I10" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="J10" t="n">
         <v>86.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="L10" t="n">
         <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="N10" t="n">
         <v>0.369</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P10" t="n">
         <v>25.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S10" t="n">
         <v>29.1</v>
@@ -2168,10 +2235,10 @@
         <v>38.4</v>
       </c>
       <c r="U10" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>9.300000000000001</v>
@@ -2180,7 +2247,7 @@
         <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
         <v>23.3</v>
@@ -2195,16 +2262,16 @@
         <v>-4</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH10" t="n">
         <v>24</v>
@@ -2228,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2246,7 +2313,7 @@
         <v>30</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J11" t="n">
         <v>84.40000000000001</v>
@@ -2329,7 +2396,7 @@
         <v>22.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O11" t="n">
         <v>19</v>
@@ -2344,19 +2411,19 @@
         <v>11.9</v>
       </c>
       <c r="S11" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T11" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
         <v>3.8</v>
@@ -2365,19 +2432,19 @@
         <v>6.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA11" t="n">
         <v>22.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.6</v>
+        <v>101.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2407,10 +2474,10 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
         <v>13</v>
@@ -2419,22 +2486,22 @@
         <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT11" t="n">
         <v>12</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2449,10 +2516,10 @@
         <v>2</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="H12" t="n">
         <v>48</v>
@@ -2499,19 +2566,19 @@
         <v>36.5</v>
       </c>
       <c r="J12" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M12" t="n">
         <v>22.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O12" t="n">
         <v>19</v>
@@ -2535,10 +2602,10 @@
         <v>20.9</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
         <v>5.5</v>
@@ -2550,16 +2617,16 @@
         <v>22.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2577,7 +2644,7 @@
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
         <v>28</v>
@@ -2589,16 +2656,16 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP12" t="n">
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
         <v>28</v>
@@ -2607,22 +2674,22 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU12" t="n">
         <v>17</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2631,7 +2698,7 @@
         <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
         <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J13" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L13" t="n">
         <v>5.8</v>
       </c>
       <c r="M13" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N13" t="n">
         <v>0.331</v>
       </c>
       <c r="O13" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P13" t="n">
         <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="R13" t="n">
         <v>11.5</v>
@@ -2714,13 +2781,13 @@
         <v>41.7</v>
       </c>
       <c r="U13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X13" t="n">
         <v>5.8</v>
@@ -2729,25 +2796,25 @@
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
         <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>22</v>
@@ -2756,7 +2823,7 @@
         <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>22</v>
@@ -2768,19 +2835,19 @@
         <v>20</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR13" t="n">
         <v>12</v>
@@ -2789,7 +2856,7 @@
         <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AU13" t="n">
         <v>9</v>
@@ -2807,13 +2874,13 @@
         <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.716</v>
+        <v>0.72</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L14" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
         <v>19</v>
       </c>
       <c r="N14" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O14" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R14" t="n">
         <v>11.7</v>
@@ -2902,7 +2969,7 @@
         <v>13.5</v>
       </c>
       <c r="W14" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
@@ -2911,19 +2978,19 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
         <v>21.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC14" t="n">
         <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2944,7 +3011,7 @@
         <v>7</v>
       </c>
       <c r="AK14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2953,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>16</v>
@@ -2983,10 +3050,10 @@
         <v>9</v>
       </c>
       <c r="AX14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
         <v>6</v>
@@ -2995,7 +3062,7 @@
         <v>13</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
         <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.521</v>
+        <v>0.514</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
       <c r="J15" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.472</v>
+        <v>0.47</v>
       </c>
       <c r="L15" t="n">
         <v>4.4</v>
@@ -3057,16 +3124,16 @@
         <v>12.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O15" t="n">
         <v>19.4</v>
       </c>
       <c r="P15" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R15" t="n">
         <v>13.1</v>
@@ -3078,19 +3145,19 @@
         <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X15" t="n">
         <v>4.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
         <v>20.1</v>
@@ -3099,13 +3166,13 @@
         <v>22.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>103.2</v>
+        <v>102.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3123,40 +3190,40 @@
         <v>3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
         <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR15" t="n">
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3165,13 +3232,13 @@
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -3180,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
         <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>0.541</v>
+        <v>0.547</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P16" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R16" t="n">
         <v>10.6</v>
@@ -3263,7 +3330,7 @@
         <v>18.9</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W16" t="n">
         <v>7.3</v>
@@ -3275,22 +3342,22 @@
         <v>4.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA16" t="n">
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.8</v>
+        <v>96</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -3308,34 +3375,34 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="n">
         <v>17</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
         <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>19</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>28</v>
@@ -3344,25 +3411,25 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
         <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>13</v>
@@ -3493,13 +3560,13 @@
         <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
         <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>30</v>
@@ -3511,7 +3578,7 @@
         <v>18</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>12</v>
@@ -3526,13 +3593,13 @@
         <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
         <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>0.189</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3591,67 +3658,67 @@
         <v>38.1</v>
       </c>
       <c r="J18" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="K18" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P18" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.745</v>
       </c>
       <c r="R18" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S18" t="n">
         <v>31.5</v>
       </c>
       <c r="T18" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U18" t="n">
         <v>19.8</v>
       </c>
       <c r="V18" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z18" t="n">
         <v>20.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
         <v>98.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3663,7 +3730,7 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
         <v>13</v>
@@ -3678,28 +3745,28 @@
         <v>26</v>
       </c>
       <c r="AM18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
         <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="n">
         <v>24</v>
@@ -3708,13 +3775,13 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
@@ -3723,7 +3790,7 @@
         <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="H19" t="n">
         <v>48</v>
@@ -3779,46 +3846,46 @@
         <v>0.426</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.324</v>
+        <v>0.322</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
         <v>24.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
         <v>10.9</v>
       </c>
       <c r="S19" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="T19" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="U19" t="n">
         <v>18.7</v>
       </c>
       <c r="V19" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W19" t="n">
         <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
         <v>20.1</v>
@@ -3830,10 +3897,10 @@
         <v>91.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3866,13 +3933,13 @@
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -3890,19 +3957,19 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
         <v>22</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
         <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>0.467</v>
+        <v>0.461</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,7 +4022,7 @@
         <v>38.5</v>
       </c>
       <c r="J20" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K20" t="n">
         <v>0.462</v>
@@ -3964,28 +4031,28 @@
         <v>7.1</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P20" t="n">
         <v>20.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.783</v>
+        <v>0.78</v>
       </c>
       <c r="R20" t="n">
         <v>10.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U20" t="n">
         <v>22.2</v>
@@ -4009,10 +4076,10 @@
         <v>19.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.3</v>
+        <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
@@ -4045,7 +4112,7 @@
         <v>8</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4057,16 +4124,16 @@
         <v>5</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
@@ -4078,19 +4145,19 @@
         <v>30</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E21" t="n">
         <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.356</v>
+        <v>0.351</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J21" t="n">
         <v>83.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O21" t="n">
         <v>16.5</v>
@@ -4170,7 +4237,7 @@
         <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V21" t="n">
         <v>14</v>
@@ -4188,28 +4255,28 @@
         <v>20.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
         <v>14</v>
@@ -4218,16 +4285,16 @@
         <v>8</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4236,25 +4303,25 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
         <v>25</v>
       </c>
       <c r="AU21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>26</v>
@@ -4263,7 +4330,7 @@
         <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>28</v>
       </c>
       <c r="G22" t="n">
-        <v>0.616</v>
+        <v>0.622</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,10 +4386,10 @@
         <v>37.1</v>
       </c>
       <c r="J22" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L22" t="n">
         <v>4.9</v>
@@ -4331,13 +4398,13 @@
         <v>14.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O22" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="P22" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0.802</v>
@@ -4346,10 +4413,10 @@
         <v>11.6</v>
       </c>
       <c r="S22" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T22" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U22" t="n">
         <v>19.9</v>
@@ -4376,13 +4443,13 @@
         <v>100.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
         <v>10</v>
@@ -4394,13 +4461,13 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="n">
         <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL22" t="n">
         <v>25</v>
@@ -4409,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -4498,19 +4565,19 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J23" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.367</v>
@@ -4522,19 +4589,19 @@
         <v>26.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.726</v>
+        <v>0.728</v>
       </c>
       <c r="R23" t="n">
         <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T23" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U23" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="V23" t="n">
         <v>14.2</v>
@@ -4546,22 +4613,22 @@
         <v>5.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>101.6</v>
+        <v>101.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4573,7 +4640,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>26</v>
@@ -4603,16 +4670,16 @@
         <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
@@ -4621,7 +4688,7 @@
         <v>27</v>
       </c>
       <c r="AX23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
@@ -4633,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
         <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,10 +4750,10 @@
         <v>37.3</v>
       </c>
       <c r="J24" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K24" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L24" t="n">
         <v>5.5</v>
@@ -4695,16 +4762,16 @@
         <v>16.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O24" t="n">
         <v>16.8</v>
       </c>
       <c r="P24" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R24" t="n">
         <v>11.8</v>
@@ -4713,7 +4780,7 @@
         <v>29.9</v>
       </c>
       <c r="T24" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U24" t="n">
         <v>20.5</v>
@@ -4737,13 +4804,13 @@
         <v>18.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>23</v>
@@ -4755,7 +4822,7 @@
         <v>24</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>19</v>
@@ -4764,16 +4831,16 @@
         <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO24" t="n">
         <v>27</v>
@@ -4782,16 +4849,16 @@
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
         <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>20</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
         <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.649</v>
+        <v>0.653</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
@@ -4874,10 +4941,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="O25" t="n">
         <v>20</v>
@@ -4892,13 +4959,13 @@
         <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U25" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V25" t="n">
         <v>14.9</v>
@@ -4910,46 +4977,46 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>110.6</v>
+        <v>110.5</v>
       </c>
       <c r="AC25" t="n">
         <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>6</v>
       </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="n">
         <v>6</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>2</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>6</v>
@@ -4958,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP25" t="n">
         <v>9</v>
@@ -4967,7 +5034,7 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
         <v>7</v>
@@ -4976,19 +5043,19 @@
         <v>8</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV25" t="n">
         <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -5032,13 +5099,13 @@
         <v>75</v>
       </c>
       <c r="E26" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5053,46 +5120,46 @@
         <v>0.461</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M26" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O26" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P26" t="n">
         <v>25.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
         <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="T26" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="W26" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
         <v>20.9</v>
@@ -5104,25 +5171,25 @@
         <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
       </c>
       <c r="AI26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
         <v>26</v>
@@ -5131,16 +5198,16 @@
         <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN26" t="n">
         <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP26" t="n">
         <v>12</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
         <v>28</v>
@@ -5179,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="BB26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC26" t="n">
         <v>11</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E27" t="n">
         <v>24</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>0.32</v>
+        <v>0.316</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J27" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L27" t="n">
         <v>6</v>
@@ -5241,34 +5308,34 @@
         <v>17.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O27" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R27" t="n">
         <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T27" t="n">
         <v>42.9</v>
       </c>
       <c r="U27" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V27" t="n">
         <v>15.2</v>
       </c>
       <c r="W27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X27" t="n">
         <v>4.6</v>
@@ -5280,13 +5347,13 @@
         <v>22.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
@@ -5295,25 +5362,25 @@
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>6</v>
       </c>
       <c r="AK27" t="n">
         <v>19</v>
       </c>
       <c r="AL27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
         <v>18</v>
@@ -5328,10 +5395,10 @@
         <v>17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS27" t="n">
         <v>14</v>
@@ -5340,10 +5407,10 @@
         <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5355,7 +5422,7 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5460,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J28" t="n">
         <v>81.3</v>
@@ -5435,7 +5502,7 @@
         <v>0.745</v>
       </c>
       <c r="R28" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S28" t="n">
         <v>31.9</v>
@@ -5444,13 +5511,13 @@
         <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X28" t="n">
         <v>4.8</v>
@@ -5459,19 +5526,19 @@
         <v>5.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA28" t="n">
         <v>20.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>12</v>
@@ -5480,19 +5547,19 @@
         <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>15</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5510,10 +5577,10 @@
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
         <v>8</v>
@@ -5525,13 +5592,13 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW28" t="n">
         <v>26</v>
       </c>
       <c r="AX28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY28" t="n">
         <v>22</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F29" t="n">
         <v>37</v>
       </c>
       <c r="G29" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J29" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L29" t="n">
         <v>6.3</v>
@@ -5608,10 +5675,10 @@
         <v>0.372</v>
       </c>
       <c r="O29" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P29" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="Q29" t="n">
         <v>0.762</v>
@@ -5620,10 +5687,10 @@
         <v>9.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U29" t="n">
         <v>21.6</v>
@@ -5641,37 +5708,37 @@
         <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB29" t="n">
         <v>103.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
         <v>17</v>
       </c>
       <c r="AF29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
         <v>6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>5</v>
@@ -5680,13 +5747,13 @@
         <v>15</v>
       </c>
       <c r="AM29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
         <v>3</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
         <v>8</v>
@@ -5695,34 +5762,34 @@
         <v>13</v>
       </c>
       <c r="AR29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT29" t="n">
         <v>24</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>26</v>
       </c>
       <c r="AU29" t="n">
         <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA29" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
         <v>50</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5787,7 +5854,7 @@
         <v>14.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O30" t="n">
         <v>20.3</v>
@@ -5796,7 +5863,7 @@
         <v>27.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R30" t="n">
         <v>10.6</v>
@@ -5805,13 +5872,13 @@
         <v>31.4</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
         <v>26.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
@@ -5820,7 +5887,7 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z30" t="n">
         <v>22.5</v>
@@ -5829,10 +5896,10 @@
         <v>22.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.1</v>
+        <v>104.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,10 +5908,10 @@
         <v>4</v>
       </c>
       <c r="AF30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH30" t="n">
         <v>27</v>
@@ -5865,7 +5932,7 @@
         <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS30" t="n">
         <v>11</v>
@@ -5892,7 +5959,7 @@
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" t="n">
         <v>52</v>
       </c>
       <c r="G31" t="n">
-        <v>0.288</v>
+        <v>0.297</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5966,7 +6033,7 @@
         <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N31" t="n">
         <v>0.343</v>
@@ -5978,22 +6045,22 @@
         <v>23.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
         <v>18.5</v>
       </c>
       <c r="V31" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
         <v>6.1</v>
@@ -6002,28 +6069,28 @@
         <v>5.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA31" t="n">
         <v>20.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>27</v>
@@ -6047,25 +6114,25 @@
         <v>23</v>
       </c>
       <c r="AN31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
         <v>23</v>
       </c>
       <c r="AP31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS31" t="n">
         <v>24</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>26</v>
-      </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>30</v>
@@ -6080,7 +6147,7 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-1-2009-10</t>
+          <t>2010-04-01</t>
         </is>
       </c>
     </row>
